--- a/final/920100_三协电机_三表抽取.xlsx
+++ b/final/920100_三协电机_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +454,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -482,6 +488,11 @@
           <t>2022 年 7 月 9 日，常州三协电机股份有限公司 2022 年度第一次临时股东大会审议通过《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》，公司向稳正景明和长泽创投定向发行股票，发行股数为530万股，每股认购价格为 4.48元/股。本次募集资金总额为2,374.40万元，以货币资金形式认缴，其中530.00 万元计入注册资本，1,844.40 万元增加资本公积。</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -511,6 +522,11 @@
           <t>2022 年 7 月 9 日，常州三协电机股份有限公司 2022 年度第一次临时股东大会审议通过《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》，公司向稳正景明和长泽创投定向发行股票，发行股数为530万股，每股认购价格为 4.48元/股。本次募集资金总额为2,374.40万元，以货币资金形式认缴，其中530.00 万元计入注册资本，1,844.40 万元增加资本公积。</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -538,6 +554,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>2023年 8月 28日，公司实际发行 318.5 万股，增发价格为 5.41 元/股，全部以货币资金形式认缴，实际募集资金总额为 1,723.09万元，其中318.5万元计入股本，1,404.59万元计入资本公积，本次发行完成后公司股本总额增至3,848.50万元，由苏亚金诚审验，于 2023年 9月 8 日出具苏亚验[2023]10号验资报告。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -552,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,6 +627,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -640,6 +666,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -674,6 +705,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -708,6 +744,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -742,6 +783,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +822,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -810,6 +861,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -844,6 +900,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -878,6 +939,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -912,6 +978,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -946,6 +1017,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -980,6 +1056,11 @@
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1010,6 +1091,1872 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>Markdown表格: 未标注时点, 比例合计100.0%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>43</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2019年5月深圳三协设立时股权结构</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>300</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>德智高新</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>153</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2019年5月深圳三协设立时股权结构</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>300</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>87</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>43</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2019年5月深圳三协设立时股权结构</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>300</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>60</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2019年 5月15日，德智高新、陆宇君、陈广武共同签署《深圳市三协电机有限公司公司章程》，设立深圳三协，注册资本为人民币 300.00万元。其中，德智高新持有 51%的股权，陆宇君持有 29%的股权，陈广武持有20%的股权。</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>44</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2019年7月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>300</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>153</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>44</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2019年7月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>300</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>87</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>44</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2019年7月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>300</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2019年 7月18日，深圳三协召开股东会，作出决议，同意股东德智高新将其所持公司 51%的股权转让给朱南保。</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>300</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>90</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>44</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>300</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>105</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>44</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>300</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>卢娇娇</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>75</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>44</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2019年12月/2020年1月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>300</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2019年 12月 4日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21%的股权转让给卢娇娇；同意股东陈广武将其所持公司4%的股权转让给卢娇娇；同意股东陈广武将其所持公司6%的股权转让给陆宇君。</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>300</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>75</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>45</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>300</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>105</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>45</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>300</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>45</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2021年5月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>300</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意股东卢娇娇将其所持公司 25%的股权转让给王洪波；同意股东朱南保将其所占公司5%的股权转让给王洪波；同意股东陈广武将其所占公司2.5%的股权转让给王洪波。</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>45</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>400</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>85</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>45</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>400</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>陆宇君</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>140</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>45</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>400</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>45</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2021年5月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>400</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2021年 5月10日，深圳三协召开股东会，作出决议，同意增加注册资本 100万元，即由原来 300 万元增加至400万元，由原股东同比例增资。其中，股东朱南保增加出资10 万元，股东陆宇君增加出资35万元，股东王洪波增加出资 55 万元。</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>45</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2022年10月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>400</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>225</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>45</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2022年10月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>400</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>王洪波</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>45</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2022年10月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>400</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2022年 10月 19日，深圳三协召开股东会，作出决议，同意股东陆宇君将其持有公司 35%的股权转让给朱南保。</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>46</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2022年11月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>400</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>225</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>46</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2022年11月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>400</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>130</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>46</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2022年11月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>400</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2022年 10月 26日，深圳三协召开股东会，作出决议，同意股东王洪波将其所持公司 32.5%的股权转让给发行人全资子公司三合融创。</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>46</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>440</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>225</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>46</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>440</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>130</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>46</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>440</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>46</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t7</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2023年3月增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>440</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2023年 3月30日，深圳三协召开股东会，全体股东一致同意将原注册资本 400万元变更为 440万元，由新股东黄晓彬认缴新增注册资本40万元。</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>46</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>440</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>46</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>440</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>440</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>46</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t8</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2023年8月股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>440</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>黄晓彬</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2023年 8月21日，深圳三协召开股东会，作出决议，同意股东朱南保将其所持公司 21.46%的股权转让给三合融创。</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>47</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t9</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2024年6月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>400</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>47</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t9</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2024年6月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>400</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t9</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2024年6月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>400</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>陈广武</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2024年 3月1日，深圳三协召开股东会，决定深圳三协注册资本由人民币 440.00万元减少至人民币400.00万元，减资后的股东变更为三合融创、朱南保、陈广武，并修改章程相应条款。</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t10</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025年7月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>370</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>三合融创</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>224.424</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025年7月减资后股权结构</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>370</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>朱南保</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>130.576</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025年 3月25日，深圳三协召开股东会，决定深圳三协注册资本由人民币400.00万元减少至人民币370.00万元，减资后的股东变更为三合融创、朱南保，并修改章程相应条款。</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>toc_located_p43-47</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>检查项</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>公司代码</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验条目</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PDF披露值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>计算值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>差异</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差异率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>是否在容差范围内</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>原文证据</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>股权结构存量</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>920100</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>三协电机 三表抽取</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>文件包含3个sheet</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>920100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>subscription=3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>transfer=10</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>920100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>各时点持股比例合计</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>100.0000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>49条快照,比例合计100.00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>全部时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>920100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>稳正景明 2022-07-09</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2022 年 7 月 9 日，常州三协电机股份有限公司 2022 年度第一次临时股东大会审议通过《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》，公司向稳正景明和长泽创投定向发行股票，发行</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>920100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>长泽创投 2022-07-09</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2022 年 7 月 9 日，常州三协电机股份有限公司 2022 年度第一次临时股东大会审议通过《关于&lt;常州三协电机股份有限公司股票定向发行说明书&gt;的议案》，公司向稳正景明和长泽创投定向发行股票，发行</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>920100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>（未披露具体认购方名称） 2023-08-28</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2023年 8月 28日，公司实际发行 318.5 万股，增发价格为 5.41 元/股，全部以货币资金形式认缴，实际募集资金总额为 1,723.09万元，其中318.5万元计入股本，1,404.59万</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>920100</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>未标注时点 (11名股东)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.0000%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>未标注时点</t>
         </is>
       </c>
     </row>
